--- a/links de interes.xlsx
+++ b/links de interes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
   <si>
     <t>Enlace</t>
   </si>
@@ -229,6 +229,24 @@
   </si>
   <si>
     <t>Escritura de código más rapida en visual studio code - snipets</t>
+  </si>
+  <si>
+    <t>https://jquery.com/download/</t>
+  </si>
+  <si>
+    <t>Jquery</t>
+  </si>
+  <si>
+    <t>https://docs.div.zone/docs/javascript/javascript-basics/dom-events</t>
+  </si>
+  <si>
+    <t>Eventos con js</t>
+  </si>
+  <si>
+    <t>https://eloquentjavascript.net/</t>
+  </si>
+  <si>
+    <t>Libro js, bunisimo</t>
   </si>
 </sst>
 </file>
@@ -558,7 +576,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:C38"/>
+  <dimension ref="B2:C41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="64.28515625" bestFit="1" customWidth="1"/>
@@ -815,49 +833,73 @@
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C33" t="s">
-        <v>51</v>
+        <v>72</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C34" t="s">
-        <v>53</v>
+        <v>74</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" t="s">
-        <v>55</v>
+        <v>70</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C41" t="s">
         <v>60</v>
       </c>
     </row>
@@ -888,19 +930,22 @@
     <hyperlink ref="B30" r:id="rId23"/>
     <hyperlink ref="B31" r:id="rId24"/>
     <hyperlink ref="B32" r:id="rId25"/>
-    <hyperlink ref="B33" r:id="rId26"/>
-    <hyperlink ref="B34" r:id="rId27"/>
-    <hyperlink ref="B35" r:id="rId28"/>
-    <hyperlink ref="B36" r:id="rId29"/>
-    <hyperlink ref="B37" r:id="rId30"/>
-    <hyperlink ref="B38" r:id="rId31"/>
+    <hyperlink ref="B36" r:id="rId26"/>
+    <hyperlink ref="B37" r:id="rId27"/>
+    <hyperlink ref="B38" r:id="rId28"/>
+    <hyperlink ref="B39" r:id="rId29"/>
+    <hyperlink ref="B40" r:id="rId30"/>
+    <hyperlink ref="B41" r:id="rId31"/>
     <hyperlink ref="B21" r:id="rId32"/>
     <hyperlink ref="B4" r:id="rId33"/>
     <hyperlink ref="B12" r:id="rId34"/>
     <hyperlink ref="B17" r:id="rId35"/>
     <hyperlink ref="B5" r:id="rId36"/>
+    <hyperlink ref="B35" r:id="rId37"/>
+    <hyperlink ref="B33" r:id="rId38"/>
+    <hyperlink ref="B34" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId37"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId40"/>
 </worksheet>
 </file>
--- a/links de interes.xlsx
+++ b/links de interes.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="84">
   <si>
     <t>Enlace</t>
   </si>
@@ -259,6 +259,18 @@
   </si>
   <si>
     <t>Aprender git jugado</t>
+  </si>
+  <si>
+    <t>https://www.bcn.cl/leychile/navegar?idNorma=1209272</t>
+  </si>
+  <si>
+    <t>La Ley 21.719 es la nueva normativa chilena de Protección de Datos Personales.</t>
+  </si>
+  <si>
+    <t>https://dbdiagram.io/home</t>
+  </si>
+  <si>
+    <t>para la creación de diagramas</t>
   </si>
 </sst>
 </file>
@@ -282,12 +294,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -303,13 +321,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -591,7 +611,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:C43"/>
+  <dimension ref="B2:C45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="64.28515625" bestFit="1" customWidth="1"/>
@@ -932,6 +952,22 @@
       </c>
       <c r="C43" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C45" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -977,8 +1013,10 @@
     <hyperlink ref="B36" r:id="rId39"/>
     <hyperlink ref="B13" r:id="rId40"/>
     <hyperlink ref="B14" r:id="rId41"/>
+    <hyperlink ref="B44" r:id="rId42"/>
+    <hyperlink ref="B45" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId42"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId44"/>
 </worksheet>
 </file>
--- a/links de interes.xlsx
+++ b/links de interes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="85">
   <si>
     <t>Enlace</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>para la creación de diagramas</t>
+  </si>
+  <si>
+    <t>https://wikiguias.digital.gob.cl/datos-personales/guia-practica-implementacion-nueva-ley-datos-personales</t>
   </si>
 </sst>
 </file>
@@ -611,7 +614,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:C45"/>
+  <dimension ref="B2:C46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="64.28515625" bestFit="1" customWidth="1"/>
@@ -968,6 +971,11 @@
       </c>
       <c r="C45" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1015,8 +1023,9 @@
     <hyperlink ref="B14" r:id="rId41"/>
     <hyperlink ref="B44" r:id="rId42"/>
     <hyperlink ref="B45" r:id="rId43"/>
+    <hyperlink ref="B46" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId44"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId45"/>
 </worksheet>
 </file>
--- a/links de interes.xlsx
+++ b/links de interes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="87">
   <si>
     <t>Enlace</t>
   </si>
@@ -274,6 +274,12 @@
   </si>
   <si>
     <t>https://wikiguias.digital.gob.cl/datos-personales/guia-practica-implementacion-nueva-ley-datos-personales</t>
+  </si>
+  <si>
+    <t>https://www.w3schools.com/sql/sql_ref_sqlserver.asp</t>
+  </si>
+  <si>
+    <t>Ejemplos de funciones de agregación y otras en SQL</t>
   </si>
 </sst>
 </file>
@@ -614,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:C46"/>
+  <dimension ref="B2:C47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="64.28515625" bestFit="1" customWidth="1"/>
@@ -976,6 +982,14 @@
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>84</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C47" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1024,8 +1038,9 @@
     <hyperlink ref="B44" r:id="rId42"/>
     <hyperlink ref="B45" r:id="rId43"/>
     <hyperlink ref="B46" r:id="rId44"/>
+    <hyperlink ref="B47" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId45"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId46"/>
 </worksheet>
 </file>
--- a/links de interes.xlsx
+++ b/links de interes.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="89">
   <si>
     <t>Enlace</t>
   </si>
@@ -280,6 +280,12 @@
   </si>
   <si>
     <t>Ejemplos de funciones de agregación y otras en SQL</t>
+  </si>
+  <si>
+    <t>https://www.w3schools.com/sql/func_mysql_curdate.asp</t>
+  </si>
+  <si>
+    <t>Otros ejemplos de funciones</t>
   </si>
 </sst>
 </file>
@@ -620,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:C47"/>
+  <dimension ref="B2:C48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="64.28515625" bestFit="1" customWidth="1"/>
@@ -990,6 +996,14 @@
       </c>
       <c r="C47" t="s">
         <v>86</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1039,8 +1053,9 @@
     <hyperlink ref="B45" r:id="rId43"/>
     <hyperlink ref="B46" r:id="rId44"/>
     <hyperlink ref="B47" r:id="rId45"/>
+    <hyperlink ref="B48" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId46"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId47"/>
 </worksheet>
 </file>